--- a/excel task 28-07.xlsx
+++ b/excel task 28-07.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library5\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C834B58-F990-42A9-B083-F6BD18845E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D4818A-96F2-43FF-B37F-09D8B3A13D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="3" xr2:uid="{B1AC5D2D-4515-4A73-9E77-F4D3FF0B2E00}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="4" xr2:uid="{B1AC5D2D-4515-4A73-9E77-F4D3FF0B2E00}"/>
   </bookViews>
   <sheets>
     <sheet name="customer" sheetId="2" r:id="rId1"/>
     <sheet name="product" sheetId="6" r:id="rId2"/>
     <sheet name="store" sheetId="3" r:id="rId3"/>
     <sheet name="sales" sheetId="4" r:id="rId4"/>
-    <sheet name="task que" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId5"/>
+    <sheet name="task que" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="183">
   <si>
     <t> Practice Tasks</t>
   </si>
@@ -939,13 +962,36 @@
   </si>
   <si>
     <t>total sales</t>
+  </si>
+  <si>
+    <t>Create a Dynamic Product Search.
+Input: Product ID
+Output: - Product Name - Category - Brand - Price - Stock</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>enter product id and get all other information</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>customer name</t>
+  </si>
+  <si>
+    <t>city</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -995,8 +1041,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1024,6 +1083,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1064,48 +1129,283 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="26">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1142,7 +1442,82 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1180,118 +1555,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1384,188 +1648,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1580,70 +1662,71 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5F942AD2-5306-406E-8A75-65A2415670A6}" name="Table7" displayName="Table7" ref="A1:E11" totalsRowShown="0" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5F942AD2-5306-406E-8A75-65A2415670A6}" name="Table7" displayName="Table7" ref="A1:E11" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A1:E11" xr:uid="{5F942AD2-5306-406E-8A75-65A2415670A6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DADCC717-E1AE-4444-AD8E-A98CDB0A56DE}" name="Customer id" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{39A30BBB-0D54-4DF1-91E2-31E8EE89D8C2}" name="Customer Name" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{9043195E-5D32-421E-B973-B8B09D5E91D7}" name="City" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{B12B11CC-912C-419B-9C69-BB99A4361BE4}" name="State" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{4EB41D40-EFDD-4655-A2CF-8E673854CFE0}" name="Gender" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{DADCC717-E1AE-4444-AD8E-A98CDB0A56DE}" name="Customer id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{39A30BBB-0D54-4DF1-91E2-31E8EE89D8C2}" name="Customer Name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{9043195E-5D32-421E-B973-B8B09D5E91D7}" name="City" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{B12B11CC-912C-419B-9C69-BB99A4361BE4}" name="State" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{4EB41D40-EFDD-4655-A2CF-8E673854CFE0}" name="Gender" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9E4CFB35-F379-41B3-A8B9-1D9628CB151F}" name="Table8" displayName="Table8" ref="A1:F11" totalsRowShown="0">
-  <autoFilter ref="A1:F11" xr:uid="{9E4CFB35-F379-41B3-A8B9-1D9628CB151F}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9E4CFB35-F379-41B3-A8B9-1D9628CB151F}" name="Table8" displayName="Table8" ref="A1:G11" totalsRowShown="0">
+  <autoFilter ref="A1:G11" xr:uid="{9E4CFB35-F379-41B3-A8B9-1D9628CB151F}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3B39501F-B46C-4375-BFE4-965A9000119F}" name="Product id"/>
     <tableColumn id="3" xr3:uid="{5A0BE9F6-30DA-4E61-B62D-240AD0E0B197}" name="Product name"/>
     <tableColumn id="4" xr3:uid="{90FABDC1-3F0A-483B-AB6F-9D417B9D13F7}" name="Category"/>
     <tableColumn id="5" xr3:uid="{6FDBF845-0E49-4607-8F5D-DB249AF5B713}" name="Brand"/>
     <tableColumn id="6" xr3:uid="{313CFBB1-E193-4D60-A45B-79AEE0D82821}" name="Price"/>
     <tableColumn id="7" xr3:uid="{A9035D16-337F-42AA-AD63-76EE9ECCB4CB}" name="Stock"/>
+    <tableColumn id="2" xr3:uid="{792A31AE-A288-4BC5-8251-E47B83AB4995}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{91D10DB0-AA2F-481B-A26F-91C5502ED080}" name="Table10" displayName="Table10" ref="A1:D6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{91D10DB0-AA2F-481B-A26F-91C5502ED080}" name="Table10" displayName="Table10" ref="A1:D6" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:D6" xr:uid="{91D10DB0-AA2F-481B-A26F-91C5502ED080}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AC4C95F9-FC2B-4C5C-97AE-6381FEADB340}" name="Store ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{8FB74DB4-C146-4FC5-95B7-62B697E6D11D}" name="Store Name" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{CF7BFF84-E0C0-48BD-B244-6490DD263335}" name="City" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{699D426A-3878-4BD0-9037-1F937F40BD31}" name="State" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{AC4C95F9-FC2B-4C5C-97AE-6381FEADB340}" name="Store ID" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{8FB74DB4-C146-4FC5-95B7-62B697E6D11D}" name="Store Name" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{CF7BFF84-E0C0-48BD-B244-6490DD263335}" name="City" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{699D426A-3878-4BD0-9037-1F937F40BD31}" name="State" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}" name="Table11" displayName="Table11" ref="A1:K16" totalsRowShown="0" headerRowDxfId="7" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}" name="Table11" displayName="Table11" ref="A1:K16" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:K16" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3652164A-F690-4642-BE52-B16AAF23254B}" name="Sale ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{7C980CF2-3AFA-433B-B9DE-8E12C923FBBC}" name="Product ID" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{FA40A350-A0DD-480B-858C-183FA1F666C6}" name="Customer ID" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{6C3FACBB-C203-4438-AE06-5534E7FC87F2}" name="Quantity" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{B7AC8BC2-391B-481A-A5D6-41740462F172}" name="Date" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{D8128F8C-F536-4E44-9F73-7D2E1365EC6C}" name="Store ID" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{A088A2E5-57DC-46C0-9425-9D6751FCF3CE}" name="product name" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{3652164A-F690-4642-BE52-B16AAF23254B}" name="Sale ID" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{7C980CF2-3AFA-433B-B9DE-8E12C923FBBC}" name="Product ID" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{FA40A350-A0DD-480B-858C-183FA1F666C6}" name="Customer ID" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3FACBB-C203-4438-AE06-5534E7FC87F2}" name="Quantity" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{B7AC8BC2-391B-481A-A5D6-41740462F172}" name="Date" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{D8128F8C-F536-4E44-9F73-7D2E1365EC6C}" name="Store ID" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{A088A2E5-57DC-46C0-9425-9D6751FCF3CE}" name="product name" dataDxfId="17">
       <calculatedColumnFormula>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{AA645FC5-939F-49C5-917B-61425D4FD4D3}" name="cutomer name" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{AA645FC5-939F-49C5-917B-61425D4FD4D3}" name="cutomer name" dataDxfId="16">
       <calculatedColumnFormula>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6BA84881-470B-4984-8E22-F25327B059D7}" name="store name" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{6BA84881-470B-4984-8E22-F25327B059D7}" name="store name" dataDxfId="15">
       <calculatedColumnFormula>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A4BCD0D9-32B2-4A4E-BEF0-892B24CFE7CC}" name="price" dataDxfId="3">
+    <tableColumn id="10" xr3:uid="{A4BCD0D9-32B2-4A4E-BEF0-892B24CFE7CC}" name="price" dataDxfId="14">
       <calculatedColumnFormula>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1A79EE65-1C48-4053-9FB2-2C2E21998D92}" name="total sales" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{1A79EE65-1C48-4053-9FB2-2C2E21998D92}" name="total sales" dataDxfId="13">
       <calculatedColumnFormula>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1968,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAA5361-991F-4163-8A73-C516D65334F8}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -1978,7 +2061,7 @@
     <col min="5" max="8" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -1995,222 +2078,192 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(A8,Table7[[#All],[Customer id]]))</f>
         <v>Rohan Gupta</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
@@ -2219,10 +2272,10 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B19" s="11"/>
+      <c r="B19" s="10"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
@@ -2231,10 +2284,10 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="11"/>
+      <c r="B22" s="10"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
@@ -2252,7 +2305,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4966C968-89A3-4D75-9041-24E70C1EF50F}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -2260,7 +2313,7 @@
     <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>154</v>
       </c>
@@ -2279,8 +2332,11 @@
       <c r="F1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -2300,7 +2356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -2320,7 +2376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -2340,7 +2396,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -2360,7 +2416,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -2380,7 +2436,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -2400,7 +2456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -2420,7 +2476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -2440,7 +2496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -2460,7 +2516,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -2480,33 +2536,33 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>VLOOKUP(A7,Table8[[#All],[Product id]:[Product name]],2)</f>
         <v>Printer</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(A7,Table8[[#All],[Product id]]))</f>
         <v>Printer</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -2515,12 +2571,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
@@ -2529,12 +2585,12 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -2543,15 +2599,15 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
+      <c r="A25" s="8"/>
     </row>
     <row r="26" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
@@ -2560,11 +2616,11 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2576,7 +2632,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0197F34F-045E-42FD-9DF4-C90419538979}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -2584,92 +2640,77 @@
     <col min="3" max="7" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -2683,36 +2724,36 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(A4,Table10[[#All],[Store ID]]))</f>
         <v>Central Store</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="11"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="10"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>INDEX(Table10[[#All],[City]],MATCH(A6,Table10[[#All],[Store ID]]))</f>
         <v>Jaipur</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="11"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="10"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>INDEX(Table10[[#All],[State]],MATCH(A3,Table10[[#All],[Store ID]]))</f>
         <v>Gujarat</v>
@@ -2734,7 +2775,7 @@
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="13" customWidth="1"/>
     <col min="5" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="11.28515625" customWidth="1"/>
@@ -2744,34 +2785,34 @@
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>169</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>171</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>172</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>174</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2779,38 +2820,38 @@
       <c r="A2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="13">
         <v>1</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>46023</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>124</v>
       </c>
       <c r="G2" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Laptop</v>
       </c>
-      <c r="H2" s="2" t="str">
+      <c r="H2" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Amit Patel</v>
       </c>
-      <c r="I2" s="2" t="str">
+      <c r="I2" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Alpha Store</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>55000</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>55000</v>
       </c>
@@ -2819,38 +2860,38 @@
       <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="13">
         <v>3</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>46024</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>126</v>
       </c>
       <c r="G3" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Mouse</v>
       </c>
-      <c r="H3" s="2" t="str">
+      <c r="H3" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Priya Shah</v>
       </c>
-      <c r="I3" s="2" t="str">
+      <c r="I3" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Beta Store</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>900</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>2700</v>
       </c>
@@ -2859,38 +2900,38 @@
       <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="13">
         <v>2</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>46025</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>128</v>
       </c>
       <c r="G4" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Headphones</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H4" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Rahul Mehta</v>
       </c>
-      <c r="I4" s="2" t="str">
+      <c r="I4" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Central Store</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>4500</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>9000</v>
       </c>
@@ -2899,38 +2940,38 @@
       <c r="A5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>46026</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>130</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Monitor</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Sneha Joshi</v>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="I5" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Digital Hub</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>16000</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>16000</v>
       </c>
@@ -2939,38 +2980,38 @@
       <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <v>2</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>46027</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>132</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Smartphone</v>
       </c>
-      <c r="H6" s="2" t="str">
+      <c r="H6" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Arjun Singh</v>
       </c>
-      <c r="I6" s="2" t="str">
+      <c r="I6" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Smart World</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>32000</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>64000</v>
       </c>
@@ -2979,38 +3020,38 @@
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <v>1</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>46028</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>124</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Office Chair</v>
       </c>
-      <c r="H7" s="2" t="str">
+      <c r="H7" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Neha Verma</v>
       </c>
-      <c r="I7" s="2" t="str">
+      <c r="I7" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Alpha Store</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>8500</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>8500</v>
       </c>
@@ -3019,38 +3060,38 @@
       <c r="A8" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <v>1</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>46029</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>126</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Printer</v>
       </c>
-      <c r="H8" s="2" t="str">
+      <c r="H8" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Rohan Gupta</v>
       </c>
-      <c r="I8" s="2" t="str">
+      <c r="I8" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Beta Store</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>12500</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>12500</v>
       </c>
@@ -3059,38 +3100,38 @@
       <c r="A9" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="13">
         <v>2</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>46030</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>128</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Webcam</v>
       </c>
-      <c r="H9" s="2" t="str">
+      <c r="H9" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Pooja Sharma</v>
       </c>
-      <c r="I9" s="2" t="str">
+      <c r="I9" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Central Store</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>3500</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>7000</v>
       </c>
@@ -3099,38 +3140,38 @@
       <c r="A10" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <v>4</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>46031</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>130</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Keyboard</v>
       </c>
-      <c r="H10" s="2" t="str">
+      <c r="H10" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Karan Desai</v>
       </c>
-      <c r="I10" s="2" t="str">
+      <c r="I10" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Digital Hub</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>1800</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>7200</v>
       </c>
@@ -3139,38 +3180,38 @@
       <c r="A11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>46032</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>132</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Office Desk</v>
       </c>
-      <c r="H11" s="2" t="str">
+      <c r="H11" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Anjali Nair</v>
       </c>
-      <c r="I11" s="2" t="str">
+      <c r="I11" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Smart World</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>12000</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>12000</v>
       </c>
@@ -3179,38 +3220,38 @@
       <c r="A12" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="13">
         <v>5</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>46033</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" t="s">
         <v>124</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Mouse</v>
       </c>
-      <c r="H12" s="2" t="str">
+      <c r="H12" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Amit Patel</v>
       </c>
-      <c r="I12" s="2" t="str">
+      <c r="I12" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Alpha Store</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>900</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>4500</v>
       </c>
@@ -3219,38 +3260,38 @@
       <c r="A13" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>46034</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" t="s">
         <v>126</v>
       </c>
       <c r="G13" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Headphones</v>
       </c>
-      <c r="H13" s="2" t="str">
+      <c r="H13" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Priya Shah</v>
       </c>
-      <c r="I13" s="2" t="str">
+      <c r="I13" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Beta Store</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>4500</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>13500</v>
       </c>
@@ -3259,38 +3300,38 @@
       <c r="A14" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <v>1</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>46035</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" t="s">
         <v>128</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Laptop</v>
       </c>
-      <c r="H14" s="2" t="str">
+      <c r="H14" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Rahul Mehta</v>
       </c>
-      <c r="I14" s="2" t="str">
+      <c r="I14" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Central Store</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>55000</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>55000</v>
       </c>
@@ -3299,38 +3340,38 @@
       <c r="A15" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13">
         <v>2</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>46036</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" t="s">
         <v>130</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Monitor</v>
       </c>
-      <c r="H15" s="2" t="str">
+      <c r="H15" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Sneha Joshi</v>
       </c>
-      <c r="I15" s="2" t="str">
+      <c r="I15" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Digital Hub</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>16000</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>32000</v>
       </c>
@@ -3339,46 +3380,43 @@
       <c r="A16" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13">
         <v>1</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>46037</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" t="s">
         <v>132</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>Smartphone</v>
       </c>
-      <c r="H16" s="2" t="str">
+      <c r="H16" t="str">
         <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</f>
         <v>Arjun Singh</v>
       </c>
-      <c r="I16" s="2" t="str">
+      <c r="I16" t="str">
         <f>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</f>
         <v>Smart World</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16">
         <f>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</f>
         <v>32000</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>32000</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I17" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>167</v>
       </c>
@@ -3386,173 +3424,173 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>168</v>
       </c>
       <c r="H21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B23" t="str">
         <f>INDEX(E21:E31,MATCH(A23,D21:D31,0))</f>
         <v>Laptop</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" ref="B24:B37" si="0">INDEX(E22:E32,MATCH(A24,D22:D32,0))</f>
         <v>Mouse</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>97</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>Headphones</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>117</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>Monitor</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B27" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>110</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>Office Chair</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>107</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>Printer</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>Webcam</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>100</v>
       </c>
       <c r="B31" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>114</v>
       </c>
       <c r="B32" t="e">
@@ -3561,7 +3599,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B33" t="e">
@@ -3570,7 +3608,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B34" t="e">
@@ -3579,7 +3617,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B35" t="e">
@@ -3588,7 +3626,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>117</v>
       </c>
       <c r="B36" t="e">
@@ -3597,7 +3635,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B37" t="e">
@@ -3614,36 +3652,468 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C39502A6-CE38-44A0-AEE3-07504115D2C1}">
-  <dimension ref="A1:A82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2E7446-3973-4A80-A17A-2AFCF2C21AC4}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="18" t="str" cm="1">
+        <f t="array" ref="C1:G1">_xlfn.XLOOKUP(Sheet2!B1,Table8[[#All],[Product id]],Table8[[#All],[Product name]:[Stock]],"not found")</f>
+        <v>Laptop</v>
+      </c>
+      <c r="D1" s="18" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E1" s="18" t="str">
+        <v>Dell</v>
+      </c>
+      <c r="F1" s="18">
+        <v>55000</v>
+      </c>
+      <c r="G1" s="18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(A7,Table11[[#All],[Sale ID]],0))</f>
+        <v>Laptop</v>
+      </c>
+      <c r="C7" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A7,Table11[[#All],[Sale ID]],0))</f>
+        <v>Electronics</v>
+      </c>
+      <c r="D7" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A7,Table11[[#All],[Sale ID]],0))</f>
+        <v>Samsung</v>
+      </c>
+      <c r="E7" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A7,Table11[[#All],[Sale ID]],0))</f>
+        <v>Amit Patel</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
+        <v>Smartphone</v>
+      </c>
+      <c r="C8" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
+        <v>Electronics</v>
+      </c>
+      <c r="D8" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
+        <v>Sony</v>
+      </c>
+      <c r="E8" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
+        <v>Priya Shah</v>
+      </c>
+      <c r="F8" t="str">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A8,Table11[[#All],[Sale ID]],0))</f>
+        <v>Surat</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
+        <v>Headphones</v>
+      </c>
+      <c r="C9" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
+        <v>Electronics</v>
+      </c>
+      <c r="D9" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
+        <v>Logitech</v>
+      </c>
+      <c r="E9" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
+        <v>Rahul Mehta</v>
+      </c>
+      <c r="F9" t="str">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A9,Table11[[#All],[Sale ID]],0))</f>
+        <v>Mumbai</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
+        <v>Keyboard</v>
+      </c>
+      <c r="C10" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
+        <v>Accessories</v>
+      </c>
+      <c r="D10" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
+        <v>HP</v>
+      </c>
+      <c r="E10" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
+        <v>Sneha Joshi</v>
+      </c>
+      <c r="F10" t="str">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A10,Table11[[#All],[Sale ID]],0))</f>
+        <v>Pune</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
+        <v>Mouse</v>
+      </c>
+      <c r="C11" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
+        <v>Accessories</v>
+      </c>
+      <c r="D11" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
+        <v>Canon</v>
+      </c>
+      <c r="E11" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
+        <v>Arjun Singh</v>
+      </c>
+      <c r="F11" t="str">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A11,Table11[[#All],[Sale ID]],0))</f>
+        <v>Jaipur</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
+        <v>Printer</v>
+      </c>
+      <c r="C12" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
+        <v>Electronics</v>
+      </c>
+      <c r="D12" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
+        <v>Green Soul</v>
+      </c>
+      <c r="E12" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
+        <v>Neha Verma</v>
+      </c>
+      <c r="F12" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A12,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
+        <v>Office Chair</v>
+      </c>
+      <c r="C13" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
+        <v>Furniture</v>
+      </c>
+      <c r="D13" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
+        <v>IKEA</v>
+      </c>
+      <c r="E13" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
+        <v>Rohan Gupta</v>
+      </c>
+      <c r="F13" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A13,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
+        <v>Office Desk</v>
+      </c>
+      <c r="C14" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
+        <v>Furniture</v>
+      </c>
+      <c r="D14" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
+        <v>LG</v>
+      </c>
+      <c r="E14" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
+        <v>Pooja Sharma</v>
+      </c>
+      <c r="F14" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A14,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
+        <v>Monitor</v>
+      </c>
+      <c r="C15" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
+        <v>Electronics</v>
+      </c>
+      <c r="D15" s="23" t="str">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
+        <v>Logitech</v>
+      </c>
+      <c r="E15" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
+        <v>Karan Desai</v>
+      </c>
+      <c r="F15" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A15,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" t="str">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
+        <v>Webcam</v>
+      </c>
+      <c r="C16" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
+        <v>Accessories</v>
+      </c>
+      <c r="D16" s="23" t="e">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E16" t="str">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
+        <v>Anjali Nair</v>
+      </c>
+      <c r="F16" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A16,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" t="e">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A17,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D17" s="23" t="e">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A17,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E17" t="e">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A17,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F17" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A17,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" t="e">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C18" t="e">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D18" s="23" t="e">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E18" t="e">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F18" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A18,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" t="e">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C19" t="e">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D19" s="23" t="e">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E19" t="e">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F19" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A19,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" t="e">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C20" t="e">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D20" s="23" t="e">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E20" t="e">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F20" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A20,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" t="e">
+        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C21" t="e">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D21" s="23" t="e">
+        <f>INDEX(Table8[Brand],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E21" t="e">
+        <f>INDEX(Table7[[#All],[Customer Name]],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F21" t="e">
+        <f>INDEX(Table10[[#All],[City]],MATCH(A21,Table11[[#All],[Sale ID]],0))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C39502A6-CE38-44A0-AEE3-07504115D2C1}">
+  <dimension ref="A1:A84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
+      <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
+      <c r="A4" s="4"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -3651,15 +4121,15 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
+      <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -3667,15 +4137,15 @@
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
+      <c r="A12" s="4"/>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
+      <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3683,15 +4153,15 @@
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="4"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -3699,15 +4169,15 @@
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="4"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
+      <c r="A22" s="4"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -3715,23 +4185,23 @@
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="4"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
+      <c r="A26" s="4"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="4"/>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -3739,15 +4209,15 @@
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
+      <c r="A30" s="4"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
+      <c r="A32" s="4"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -3755,15 +4225,15 @@
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
+      <c r="A34" s="4"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
+      <c r="A36" s="4"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -3771,15 +4241,15 @@
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
+      <c r="A40" s="4"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -3787,23 +4257,23 @@
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
+      <c r="A42" s="4"/>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
+      <c r="A44" s="4"/>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
+      <c r="A46" s="4"/>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -3811,15 +4281,15 @@
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
+      <c r="A48" s="4"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="5"/>
+      <c r="A50" s="4"/>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
@@ -3827,15 +4297,15 @@
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
+      <c r="A52" s="4"/>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5"/>
+      <c r="A54" s="4"/>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
@@ -3843,23 +4313,23 @@
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5"/>
+      <c r="A56" s="4"/>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="5"/>
+      <c r="A58" s="4"/>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
+      <c r="A60" s="4"/>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
@@ -3867,15 +4337,15 @@
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
+      <c r="A62" s="4"/>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
+      <c r="A64" s="4"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
@@ -3883,15 +4353,15 @@
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="5"/>
+      <c r="A66" s="4"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="5"/>
+      <c r="A68" s="4"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
@@ -3899,15 +4369,15 @@
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="5"/>
+      <c r="A70" s="4"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="5"/>
+      <c r="A72" s="4"/>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
@@ -3915,15 +4385,15 @@
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="5"/>
+      <c r="A74" s="4"/>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="5"/>
+      <c r="A76" s="4"/>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
@@ -3931,15 +4401,15 @@
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="5"/>
+      <c r="A78" s="4"/>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="5"/>
+      <c r="A80" s="4"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
@@ -3949,6 +4419,11 @@
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="240" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/excel task 28-07.xlsx
+++ b/excel task 28-07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library5\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D4818A-96F2-43FF-B37F-09D8B3A13D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5506A0-6D27-44BA-8FFF-9321B7BD1E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="4" xr2:uid="{B1AC5D2D-4515-4A73-9E77-F4D3FF0B2E00}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="3" xr2:uid="{B1AC5D2D-4515-4A73-9E77-F4D3FF0B2E00}"/>
   </bookViews>
   <sheets>
     <sheet name="customer" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="185">
   <si>
     <t> Practice Tasks</t>
   </si>
@@ -985,6 +985,12 @@
   </si>
   <si>
     <t>city</t>
+  </si>
+  <si>
+    <t>INDEX(sales!,[Category]],MATCH(Sheet2!A7,Table11[[#All],[Sale ID]],0))</t>
+  </si>
+  <si>
+    <t>CATEGORY</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1174,18 +1180,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1205,6 +1226,139 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1364,24 +1518,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
         <name val="Consolas"/>
         <family val="3"/>
         <scheme val="none"/>
@@ -1423,82 +1559,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1536,26 +1598,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1611,24 +1653,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1662,14 +1686,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5F942AD2-5306-406E-8A75-65A2415670A6}" name="Table7" displayName="Table7" ref="A1:E11" totalsRowShown="0" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5F942AD2-5306-406E-8A75-65A2415670A6}" name="Table7" displayName="Table7" ref="A1:E11" totalsRowShown="0" dataDxfId="26">
   <autoFilter ref="A1:E11" xr:uid="{5F942AD2-5306-406E-8A75-65A2415670A6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DADCC717-E1AE-4444-AD8E-A98CDB0A56DE}" name="Customer id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{39A30BBB-0D54-4DF1-91E2-31E8EE89D8C2}" name="Customer Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{9043195E-5D32-421E-B973-B8B09D5E91D7}" name="City" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B12B11CC-912C-419B-9C69-BB99A4361BE4}" name="State" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{4EB41D40-EFDD-4655-A2CF-8E673854CFE0}" name="Gender" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{DADCC717-E1AE-4444-AD8E-A98CDB0A56DE}" name="Customer id" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{39A30BBB-0D54-4DF1-91E2-31E8EE89D8C2}" name="Customer Name" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{9043195E-5D32-421E-B973-B8B09D5E91D7}" name="City" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{B12B11CC-912C-419B-9C69-BB99A4361BE4}" name="State" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{4EB41D40-EFDD-4655-A2CF-8E673854CFE0}" name="Gender" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1685,49 +1709,52 @@
     <tableColumn id="5" xr3:uid="{6FDBF845-0E49-4607-8F5D-DB249AF5B713}" name="Brand"/>
     <tableColumn id="6" xr3:uid="{313CFBB1-E193-4D60-A45B-79AEE0D82821}" name="Price"/>
     <tableColumn id="7" xr3:uid="{A9035D16-337F-42AA-AD63-76EE9ECCB4CB}" name="Stock"/>
-    <tableColumn id="2" xr3:uid="{792A31AE-A288-4BC5-8251-E47B83AB4995}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{792A31AE-A288-4BC5-8251-E47B83AB4995}" name="Column1" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{91D10DB0-AA2F-481B-A26F-91C5502ED080}" name="Table10" displayName="Table10" ref="A1:D6" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{91D10DB0-AA2F-481B-A26F-91C5502ED080}" name="Table10" displayName="Table10" ref="A1:D6" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:D6" xr:uid="{91D10DB0-AA2F-481B-A26F-91C5502ED080}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AC4C95F9-FC2B-4C5C-97AE-6381FEADB340}" name="Store ID" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{8FB74DB4-C146-4FC5-95B7-62B697E6D11D}" name="Store Name" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{CF7BFF84-E0C0-48BD-B244-6490DD263335}" name="City" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{699D426A-3878-4BD0-9037-1F937F40BD31}" name="State" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{AC4C95F9-FC2B-4C5C-97AE-6381FEADB340}" name="Store ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{8FB74DB4-C146-4FC5-95B7-62B697E6D11D}" name="Store Name" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{CF7BFF84-E0C0-48BD-B244-6490DD263335}" name="City" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{699D426A-3878-4BD0-9037-1F937F40BD31}" name="State" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}" name="Table11" displayName="Table11" ref="A1:K16" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="A1:K16" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3652164A-F690-4642-BE52-B16AAF23254B}" name="Sale ID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{7C980CF2-3AFA-433B-B9DE-8E12C923FBBC}" name="Product ID" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{FA40A350-A0DD-480B-858C-183FA1F666C6}" name="Customer ID" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3FACBB-C203-4438-AE06-5534E7FC87F2}" name="Quantity" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{B7AC8BC2-391B-481A-A5D6-41740462F172}" name="Date" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{D8128F8C-F536-4E44-9F73-7D2E1365EC6C}" name="Store ID" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{A088A2E5-57DC-46C0-9425-9D6751FCF3CE}" name="product name" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}" name="Table11" displayName="Table11" ref="A1:L16" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L16" xr:uid="{0EAA1E67-2072-43C6-808D-2BB248757921}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{3652164A-F690-4642-BE52-B16AAF23254B}" name="Sale ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{7C980CF2-3AFA-433B-B9DE-8E12C923FBBC}" name="Product ID" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{FA40A350-A0DD-480B-858C-183FA1F666C6}" name="Customer ID" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6C3FACBB-C203-4438-AE06-5534E7FC87F2}" name="Quantity" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{B7AC8BC2-391B-481A-A5D6-41740462F172}" name="Date" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{D8128F8C-F536-4E44-9F73-7D2E1365EC6C}" name="Store ID" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{A088A2E5-57DC-46C0-9425-9D6751FCF3CE}" name="product name" dataDxfId="5">
       <calculatedColumnFormula>INDEX(Table8[[#All],[Product name]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{AA645FC5-939F-49C5-917B-61425D4FD4D3}" name="cutomer name" dataDxfId="16">
+    <tableColumn id="8" xr3:uid="{AA645FC5-939F-49C5-917B-61425D4FD4D3}" name="cutomer name" dataDxfId="4">
       <calculatedColumnFormula>INDEX(Table7[[#All],[Customer Name]],MATCH(Table11[[#This Row],[Customer ID]],Table7[[#All],[Customer id]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6BA84881-470B-4984-8E22-F25327B059D7}" name="store name" dataDxfId="15">
+    <tableColumn id="9" xr3:uid="{6BA84881-470B-4984-8E22-F25327B059D7}" name="store name" dataDxfId="3">
       <calculatedColumnFormula>INDEX(Table10[[#All],[Store Name]],MATCH(Table11[[#This Row],[Store ID]],Table10[[#All],[Store ID]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A4BCD0D9-32B2-4A4E-BEF0-892B24CFE7CC}" name="price" dataDxfId="14">
+    <tableColumn id="10" xr3:uid="{A4BCD0D9-32B2-4A4E-BEF0-892B24CFE7CC}" name="price" dataDxfId="2">
       <calculatedColumnFormula>INDEX(Table8[[#All],[Price]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Product id]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1A79EE65-1C48-4053-9FB2-2C2E21998D92}" name="total sales" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{1A79EE65-1C48-4053-9FB2-2C2E21998D92}" name="total sales" dataDxfId="1">
       <calculatedColumnFormula>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{2EBA5534-90C0-4163-89C8-35C15211E7A3}" name="CATEGORY" dataDxfId="0">
+      <calculatedColumnFormula>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2769,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6286118-EEF8-4DFE-8963-EAA2D316882D}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2781,7 +2808,7 @@
     <col min="9" max="9" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2815,8 +2842,11 @@
       <c r="K1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>139</v>
       </c>
@@ -2855,8 +2885,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>55000</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
@@ -2895,8 +2929,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>2700</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
@@ -2935,8 +2973,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>9000</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>142</v>
       </c>
@@ -2975,8 +3017,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>16000</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
@@ -3015,8 +3061,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>64000</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -3055,8 +3105,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>8500</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>145</v>
       </c>
@@ -3095,8 +3149,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>12500</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>146</v>
       </c>
@@ -3135,8 +3193,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>7000</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>147</v>
       </c>
@@ -3175,8 +3237,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>7200</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>148</v>
       </c>
@@ -3215,8 +3281,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>12000</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>149</v>
       </c>
@@ -3255,8 +3325,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>4500</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>150</v>
       </c>
@@ -3295,8 +3369,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>13500</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>151</v>
       </c>
@@ -3335,8 +3413,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>55000</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>152</v>
       </c>
@@ -3375,8 +3457,12 @@
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>32000</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>153</v>
       </c>
@@ -3414,6 +3500,10 @@
       <c r="K16">
         <f>(Table11[[#This Row],[price]]*Table11[[#This Row],[Quantity]])</f>
         <v>32000</v>
+      </c>
+      <c r="L16" s="23" t="str">
+        <f>INDEX(Table8[[#All],[Category]],MATCH(Table11[[#This Row],[Product ID]],Table8[[#All],[Category]]))</f>
+        <v>Accessories</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3664,23 +3754,23 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" s="18" t="str" cm="1">
         <f t="array" ref="C1:G1">_xlfn.XLOOKUP(Sheet2!B1,Table8[[#All],[Product id]],Table8[[#All],[Product name]:[Stock]],"not found")</f>
-        <v>Laptop</v>
+        <v>Smartphone</v>
       </c>
       <c r="D1" s="18" t="str">
         <v>Electronics</v>
       </c>
       <c r="E1" s="18" t="str">
-        <v>Dell</v>
+        <v>Samsung</v>
       </c>
       <c r="F1" s="18">
-        <v>55000</v>
+        <v>32000</v>
       </c>
       <c r="G1" s="18">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3716,14 +3806,13 @@
         <v>139</v>
       </c>
       <c r="B7" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(A7,Table11[[#All],[Sale ID]],0))</f>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A7,Table11[[#All],[Sale ID]],0))</f>
         <v>Laptop</v>
       </c>
-      <c r="C7" t="str">
-        <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A7,Table11[[#All],[Sale ID]],0))</f>
-        <v>Electronics</v>
-      </c>
-      <c r="D7" s="23" t="str">
+      <c r="C7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A7,Table11[[#All],[Sale ID]],0))</f>
         <v>Samsung</v>
       </c>
@@ -3737,14 +3826,14 @@
         <v>140</v>
       </c>
       <c r="B8" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
-        <v>Smartphone</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A8,Table11[[#All],[Sale ID]],0))</f>
+        <v>Mouse</v>
       </c>
       <c r="C8" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
         <v>Electronics</v>
       </c>
-      <c r="D8" s="23" t="str">
+      <c r="D8" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A8,Table11[[#All],[Sale ID]],0))</f>
         <v>Sony</v>
       </c>
@@ -3762,14 +3851,14 @@
         <v>141</v>
       </c>
       <c r="B9" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A9,Table11[[#All],[Sale ID]],0))</f>
         <v>Headphones</v>
       </c>
       <c r="C9" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
         <v>Electronics</v>
       </c>
-      <c r="D9" s="23" t="str">
+      <c r="D9" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A9,Table11[[#All],[Sale ID]],0))</f>
         <v>Logitech</v>
       </c>
@@ -3787,14 +3876,14 @@
         <v>142</v>
       </c>
       <c r="B10" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
-        <v>Keyboard</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A10,Table11[[#All],[Sale ID]],0))</f>
+        <v>Monitor</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
         <v>Accessories</v>
       </c>
-      <c r="D10" s="23" t="str">
+      <c r="D10" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A10,Table11[[#All],[Sale ID]],0))</f>
         <v>HP</v>
       </c>
@@ -3812,14 +3901,14 @@
         <v>143</v>
       </c>
       <c r="B11" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
-        <v>Mouse</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A11,Table11[[#All],[Sale ID]],0))</f>
+        <v>Smartphone</v>
       </c>
       <c r="C11" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
         <v>Accessories</v>
       </c>
-      <c r="D11" s="23" t="str">
+      <c r="D11" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A11,Table11[[#All],[Sale ID]],0))</f>
         <v>Canon</v>
       </c>
@@ -3837,14 +3926,14 @@
         <v>144</v>
       </c>
       <c r="B12" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
-        <v>Printer</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A12,Table11[[#All],[Sale ID]],0))</f>
+        <v>Office Chair</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
         <v>Electronics</v>
       </c>
-      <c r="D12" s="23" t="str">
+      <c r="D12" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A12,Table11[[#All],[Sale ID]],0))</f>
         <v>Green Soul</v>
       </c>
@@ -3862,14 +3951,14 @@
         <v>145</v>
       </c>
       <c r="B13" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
-        <v>Office Chair</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A13,Table11[[#All],[Sale ID]],0))</f>
+        <v>Printer</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
         <v>Furniture</v>
       </c>
-      <c r="D13" s="23" t="str">
+      <c r="D13" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A13,Table11[[#All],[Sale ID]],0))</f>
         <v>IKEA</v>
       </c>
@@ -3887,14 +3976,14 @@
         <v>146</v>
       </c>
       <c r="B14" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
-        <v>Office Desk</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A14,Table11[[#All],[Sale ID]],0))</f>
+        <v>Webcam</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
         <v>Furniture</v>
       </c>
-      <c r="D14" s="23" t="str">
+      <c r="D14" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A14,Table11[[#All],[Sale ID]],0))</f>
         <v>LG</v>
       </c>
@@ -3912,14 +4001,14 @@
         <v>147</v>
       </c>
       <c r="B15" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
-        <v>Monitor</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A15,Table11[[#All],[Sale ID]],0))</f>
+        <v>Keyboard</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
         <v>Electronics</v>
       </c>
-      <c r="D15" s="23" t="str">
+      <c r="D15" s="22" t="str">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A15,Table11[[#All],[Sale ID]],0))</f>
         <v>Logitech</v>
       </c>
@@ -3937,14 +4026,14 @@
         <v>148</v>
       </c>
       <c r="B16" t="str">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
-        <v>Webcam</v>
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A16,Table11[[#All],[Sale ID]],0))</f>
+        <v>Office Desk</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
         <v>Accessories</v>
       </c>
-      <c r="D16" s="23" t="e">
+      <c r="D16" s="22" t="e">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A16,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
@@ -3958,14 +4047,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B17" t="e">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A17,Table11[[#All],[Sale ID]],0))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D17" s="23" t="e">
+      <c r="B17" t="str">
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A17,Table11[[#All],[Sale ID]],0))</f>
+        <v>Mouse</v>
+      </c>
+      <c r="D17" s="22" t="e">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A17,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
@@ -3982,15 +4071,15 @@
       <c r="A18" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B18" t="e">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
-        <v>#REF!</v>
+      <c r="B18" t="str">
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A18,Table11[[#All],[Sale ID]],0))</f>
+        <v>Headphones</v>
       </c>
       <c r="C18" t="e">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
-      <c r="D18" s="23" t="e">
+      <c r="D18" s="22" t="e">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A18,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
@@ -4007,15 +4096,15 @@
       <c r="A19" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B19" t="e">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
-        <v>#REF!</v>
+      <c r="B19" t="str">
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A19,Table11[[#All],[Sale ID]],0))</f>
+        <v>Laptop</v>
       </c>
       <c r="C19" t="e">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
-      <c r="D19" s="23" t="e">
+      <c r="D19" s="22" t="e">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A19,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
@@ -4032,15 +4121,15 @@
       <c r="A20" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="B20" t="e">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
-        <v>#REF!</v>
+      <c r="B20" t="str">
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A20,Table11[[#All],[Sale ID]],0))</f>
+        <v>Monitor</v>
       </c>
       <c r="C20" t="e">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
-      <c r="D20" s="23" t="e">
+      <c r="D20" s="22" t="e">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A20,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
@@ -4057,15 +4146,15 @@
       <c r="A21" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B21" t="e">
-        <f>INDEX(Table8[[#All],[Product name]],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
-        <v>#REF!</v>
+      <c r="B21" t="str">
+        <f>INDEX(Table11[[#All],[product name]],MATCH(A21,Table11[[#All],[Sale ID]],0))</f>
+        <v>Smartphone</v>
       </c>
       <c r="C21" t="e">
         <f>INDEX(Table8[[#All],[Category]],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
-      <c r="D21" s="23" t="e">
+      <c r="D21" s="22" t="e">
         <f>INDEX(Table8[Brand],MATCH(Sheet2!A21,Table11[[#All],[Sale ID]],0))</f>
         <v>#REF!</v>
       </c>
